--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Deco.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Deco.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -86,6 +86,45 @@
   </si>
   <si>
     <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">건설 연석</t>
+  </si>
+  <si>
+    <t xml:space="preserve">construction curb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">建設の縁石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">통나무 연석</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log curb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">丸太の縁石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">벽돌 연석</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brick curb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">煉瓦の縁石</t>
   </si>
 </sst>
 </file>
@@ -314,7 +353,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
@@ -427,16 +466,67 @@
         <v>20</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
